--- a/forms/trg/Formulir_TRG_mhvp.xlsx
+++ b/forms/trg/Formulir_TRG_mhvp.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Ariyanti Saleh, SKp. M.Si</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Faculty of Nursing, Hasanuddin University</t>
@@ -959,7 +963,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1000,7 +1004,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1045,7 +1049,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1090,7 +1094,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1135,7 +1139,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1164,7 +1168,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1205,7 +1209,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1246,7 +1250,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1279,7 +1283,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1320,7 +1324,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1361,7 +1365,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
